--- a/plate3d/PLATE3D_TANK.xlsx
+++ b/plate3d/PLATE3D_TANK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="86">
   <si>
     <t>Tank - after Billy Hau, billyhau.hk</t>
   </si>
@@ -187,6 +187,12 @@
     <t>XZ</t>
   </si>
   <si>
+    <t>pl.tr.end_1</t>
+  </si>
+  <si>
+    <t>pl.tr.end_2</t>
+  </si>
+  <si>
     <t>BASE</t>
   </si>
   <si>
@@ -194,6 +200,12 @@
   </si>
   <si>
     <t>md.body</t>
+  </si>
+  <si>
+    <t>pl.bd.tab_1</t>
+  </si>
+  <si>
+    <t>pl.bd.tab_2</t>
   </si>
   <si>
     <t>ROT.X</t>
@@ -1199,7 +1211,7 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s">
         <v>20</v>
@@ -1228,7 +1240,7 @@
         <v>56</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
@@ -1257,7 +1269,7 @@
         <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s">
         <v>18</v>
@@ -1297,13 +1309,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
         <v>23</v>
@@ -1332,7 +1344,7 @@
         <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -1361,10 +1373,10 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s">
         <v>20</v>
@@ -1390,10 +1402,10 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="E33" t="s">
         <v>20</v>
@@ -1419,10 +1431,10 @@
         <v>55</v>
       </c>
       <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
         <v>60</v>
-      </c>
-      <c r="D34" t="s">
-        <v>58</v>
       </c>
       <c r="E34" t="s">
         <v>23</v>
@@ -1460,21 +1472,21 @@
         <v>53</v>
       </c>
       <c r="J36" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K36" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
         <v>45</v>
@@ -1492,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1509,7 +1521,7 @@
         <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -1527,7 +1539,7 @@
         <v>15.529</v>
       </c>
       <c r="I38" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -1544,7 +1556,7 @@
         <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D39" t="s">
         <v>47</v>
@@ -1562,7 +1574,7 @@
         <v>24.07</v>
       </c>
       <c r="I39" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -1579,7 +1591,7 @@
         <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
         <v>48</v>
@@ -1597,7 +1609,7 @@
         <v>30.541</v>
       </c>
       <c r="I40" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -1614,10 +1626,10 @@
         <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
         <v>45</v>
@@ -1631,25 +1643,25 @@
         <v>11</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F43" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H43" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I43" t="s">
         <v>53</v>
@@ -1657,19 +1669,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1686,16 +1698,16 @@
         <v>11</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -1709,19 +1721,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
         <v>56</v>
       </c>
       <c r="E47" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1738,16 +1750,16 @@
         <v>11</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1767,16 +1779,16 @@
         <v>11</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" t="s">
         <v>79</v>
-      </c>
-      <c r="D50" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" t="s">
-        <v>75</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1793,16 +1805,16 @@
         <v>11</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F52">
         <v>-10.796</v>
@@ -1819,11 +1831,11 @@
         <v>11</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_TANK.xlsx
+++ b/plate3d/PLATE3D_TANK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="93">
   <si>
     <t>Tank - after Billy Hau, billyhau.hk</t>
   </si>
@@ -266,6 +266,27 @@
   </si>
   <si>
     <t>as.cannon</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>TANK - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -662,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -924,6 +945,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
@@ -964,6 +986,7 @@
         <v>30</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>31</v>
@@ -1042,6 +1065,7 @@
         <v>30</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>40</v>
@@ -1142,6 +1166,7 @@
         <v>52</v>
       </c>
     </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>11</v>
@@ -1278,6 +1303,7 @@
         <v>20</v>
       </c>
     </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>11</v>
@@ -1443,6 +1469,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
@@ -1638,6 +1665,7 @@
         <v>20</v>
       </c>
     </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>11</v>
@@ -1719,6 +1747,7 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>80</v>
@@ -1774,6 +1803,7 @@
         <v>57</v>
       </c>
     </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>11</v>
@@ -1800,6 +1830,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>11</v>
@@ -1826,12 +1857,47 @@
         <v>42.059</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="3" t="s">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>85</v>
+      </c>
+      <c r="C54" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" t="s">
+        <v>86</v>
+      </c>
+      <c r="G54">
+        <v>50</v>
+      </c>
+      <c r="H54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_TANK.xlsx
+++ b/plate3d/PLATE3D_TANK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="86">
   <si>
     <t>Tank - after Billy Hau, billyhau.hk</t>
   </si>
@@ -266,27 +266,6 @@
   </si>
   <si>
     <t>as.cannon</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>TANK - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -683,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -945,7 +924,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
@@ -986,7 +964,6 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>31</v>
@@ -1065,7 +1042,6 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>40</v>
@@ -1166,7 +1142,6 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>11</v>
@@ -1303,7 +1278,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>11</v>
@@ -1469,7 +1443,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
@@ -1665,7 +1638,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>11</v>
@@ -1747,7 +1719,6 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>80</v>
@@ -1803,7 +1774,6 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>11</v>
@@ -1830,7 +1800,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>11</v>
@@ -1857,47 +1826,12 @@
         <v>42.059</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C54" t="s">
-        <v>78</v>
-      </c>
-      <c r="D54" t="s">
-        <v>86</v>
-      </c>
-      <c r="G54">
-        <v>50</v>
-      </c>
-      <c r="H54" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" t="s">
-        <v>90</v>
-      </c>
-      <c r="E55">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
